--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
   <si>
     <t>Property</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t xml:space="preserve"> SNR</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -57,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,94 +429,94 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>15</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -527,26 +524,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -598,112 +595,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>36</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>70</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -715,126 +712,126 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="S2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG2" t="s" s="2">
+      <c r="AH2" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
         <v>7</v>
@@ -845,65 +842,65 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AG3" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-SNR.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
